--- a/artfynd/A 2486-2026 artfynd.xlsx
+++ b/artfynd/A 2486-2026 artfynd.xlsx
@@ -1262,10 +1262,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131009297</v>
+        <v>131009283</v>
       </c>
       <c r="B7" t="n">
-        <v>57884</v>
+        <v>79243</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1273,42 +1273,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Grössjöbergen, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>589752</v>
+        <v>589968</v>
       </c>
       <c r="R7" t="n">
-        <v>6911214</v>
+        <v>6911120</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1340,7 +1332,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1350,12 +1342,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:18</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>färska ringhack på tall</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1382,7 +1369,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131009287</v>
+        <v>131009297</v>
       </c>
       <c r="B8" t="n">
         <v>57884</v>
@@ -1425,10 +1412,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>589835</v>
+        <v>589752</v>
       </c>
       <c r="R8" t="n">
-        <v>6911210</v>
+        <v>6911214</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1460,7 +1447,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1470,7 +1457,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1502,7 +1489,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131009270</v>
+        <v>131009287</v>
       </c>
       <c r="B9" t="n">
         <v>57884</v>
@@ -1545,10 +1532,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>589700</v>
+        <v>589835</v>
       </c>
       <c r="R9" t="n">
-        <v>6911274</v>
+        <v>6911210</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1580,7 +1567,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1590,7 +1577,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1622,10 +1609,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131009283</v>
+        <v>131009270</v>
       </c>
       <c r="B10" t="n">
-        <v>79243</v>
+        <v>57884</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1633,34 +1620,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Grössjöbergen, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>589968</v>
+        <v>589700</v>
       </c>
       <c r="R10" t="n">
-        <v>6911120</v>
+        <v>6911274</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1692,7 +1687,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1702,7 +1697,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1849,53 +1849,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131009284</v>
+        <v>131009303</v>
       </c>
       <c r="B12" t="n">
-        <v>57884</v>
+        <v>80252</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Grössjöbergen, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>589966</v>
+        <v>589748</v>
       </c>
       <c r="R12" t="n">
-        <v>6911126</v>
+        <v>6911130</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1927,7 +1919,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1937,12 +1929,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:01</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>färska ringhack på tall</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1969,45 +1956,53 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131009303</v>
+        <v>131009284</v>
       </c>
       <c r="B13" t="n">
-        <v>80252</v>
+        <v>57884</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Grössjöbergen, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>589748</v>
+        <v>589966</v>
       </c>
       <c r="R13" t="n">
-        <v>6911130</v>
+        <v>6911126</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2039,7 +2034,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2049,7 +2044,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>11:01</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -3862,53 +3862,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131009302</v>
+        <v>131009285</v>
       </c>
       <c r="B29" t="n">
-        <v>57884</v>
+        <v>80252</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Grössjöbergen, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>589716</v>
+        <v>589879</v>
       </c>
       <c r="R29" t="n">
-        <v>6911140</v>
+        <v>6911153</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3940,7 +3932,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3950,12 +3942,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>09:54</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>färska ringhack på tall</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3982,7 +3969,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131009306</v>
+        <v>131009302</v>
       </c>
       <c r="B30" t="n">
         <v>57884</v>
@@ -4025,10 +4012,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>589791</v>
+        <v>589716</v>
       </c>
       <c r="R30" t="n">
-        <v>6911148</v>
+        <v>6911140</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4060,7 +4047,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4070,12 +4057,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>färska och äldre ringhack på tall</t>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4102,45 +4089,53 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131009285</v>
+        <v>131009306</v>
       </c>
       <c r="B31" t="n">
-        <v>80252</v>
+        <v>57884</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Grössjöbergen, Mpd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>589879</v>
+        <v>589791</v>
       </c>
       <c r="R31" t="n">
-        <v>6911153</v>
+        <v>6911148</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4172,7 +4167,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4182,7 +4177,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:38</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD31" t="b">

--- a/artfynd/A 2486-2026 artfynd.xlsx
+++ b/artfynd/A 2486-2026 artfynd.xlsx
@@ -915,53 +915,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131009298</v>
+        <v>131009286</v>
       </c>
       <c r="B4" t="n">
-        <v>57884</v>
+        <v>80252</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Grössjöbergen, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>589735</v>
+        <v>589865</v>
       </c>
       <c r="R4" t="n">
-        <v>6911227</v>
+        <v>6911173</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,7 +985,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1003,12 +995,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:12</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>färska ringhack på tall</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1035,7 +1022,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131009294</v>
+        <v>131009298</v>
       </c>
       <c r="B5" t="n">
         <v>57884</v>
@@ -1078,10 +1065,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>589787</v>
+        <v>589735</v>
       </c>
       <c r="R5" t="n">
-        <v>6911183</v>
+        <v>6911227</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1113,7 +1100,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1123,7 +1110,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1155,45 +1142,53 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131009286</v>
+        <v>131009294</v>
       </c>
       <c r="B6" t="n">
-        <v>80252</v>
+        <v>57884</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Grössjöbergen, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>589865</v>
+        <v>589787</v>
       </c>
       <c r="R6" t="n">
-        <v>6911173</v>
+        <v>6911183</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1225,7 +1220,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1235,7 +1230,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:24</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -2916,10 +2916,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131009308</v>
+        <v>131009305</v>
       </c>
       <c r="B21" t="n">
-        <v>79243</v>
+        <v>57884</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2927,34 +2927,42 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Grössjöbergen, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>589686</v>
+        <v>589757</v>
       </c>
       <c r="R21" t="n">
-        <v>6911077</v>
+        <v>6911178</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2986,7 +2994,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2996,7 +3004,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:43</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3023,7 +3036,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131009305</v>
+        <v>131009498</v>
       </c>
       <c r="B22" t="n">
         <v>57884</v>
@@ -3066,10 +3079,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>589757</v>
+        <v>589629</v>
       </c>
       <c r="R22" t="n">
-        <v>6911178</v>
+        <v>6911040</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3101,7 +3114,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3111,7 +3124,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -3143,10 +3156,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131009498</v>
+        <v>131009308</v>
       </c>
       <c r="B23" t="n">
-        <v>57884</v>
+        <v>79243</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3154,42 +3167,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Grössjöbergen, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>589629</v>
+        <v>589686</v>
       </c>
       <c r="R23" t="n">
-        <v>6911040</v>
+        <v>6911077</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3221,7 +3226,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3231,12 +3236,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>09:02</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>färska ringhack på tall</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -5036,53 +5036,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131009275</v>
+        <v>131009291</v>
       </c>
       <c r="B39" t="n">
-        <v>57884</v>
+        <v>80252</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Grössjöbergen, Mpd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>589844</v>
+        <v>589791</v>
       </c>
       <c r="R39" t="n">
-        <v>6911365</v>
+        <v>6911200</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5114,7 +5106,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5124,12 +5116,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:53</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>färska ringhack på tall</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5156,45 +5143,53 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131009291</v>
+        <v>131009275</v>
       </c>
       <c r="B40" t="n">
-        <v>80252</v>
+        <v>57884</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Grössjöbergen, Mpd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>589791</v>
+        <v>589844</v>
       </c>
       <c r="R40" t="n">
-        <v>6911200</v>
+        <v>6911365</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5226,7 +5221,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5236,7 +5231,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>11:53</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD40" t="b">

--- a/artfynd/A 2486-2026 artfynd.xlsx
+++ b/artfynd/A 2486-2026 artfynd.xlsx
@@ -915,45 +915,53 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131009286</v>
+        <v>131009298</v>
       </c>
       <c r="B4" t="n">
-        <v>80252</v>
+        <v>57884</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Grössjöbergen, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>589865</v>
+        <v>589735</v>
       </c>
       <c r="R4" t="n">
-        <v>6911173</v>
+        <v>6911227</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -985,7 +993,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -995,7 +1003,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:12</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1022,7 +1035,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131009298</v>
+        <v>131009294</v>
       </c>
       <c r="B5" t="n">
         <v>57884</v>
@@ -1065,10 +1078,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>589735</v>
+        <v>589787</v>
       </c>
       <c r="R5" t="n">
-        <v>6911227</v>
+        <v>6911183</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1100,7 +1113,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1110,7 +1123,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1142,53 +1155,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131009294</v>
+        <v>131009286</v>
       </c>
       <c r="B6" t="n">
-        <v>57884</v>
+        <v>80253</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Grössjöbergen, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>589787</v>
+        <v>589865</v>
       </c>
       <c r="R6" t="n">
-        <v>6911183</v>
+        <v>6911173</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1220,7 +1225,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1230,12 +1235,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:24</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>färska ringhack på tall</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1265,7 +1265,7 @@
         <v>131009283</v>
       </c>
       <c r="B7" t="n">
-        <v>79243</v>
+        <v>79244</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1849,45 +1849,53 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131009303</v>
+        <v>131009284</v>
       </c>
       <c r="B12" t="n">
-        <v>80252</v>
+        <v>57884</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Grössjöbergen, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>589748</v>
+        <v>589966</v>
       </c>
       <c r="R12" t="n">
-        <v>6911130</v>
+        <v>6911126</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1919,7 +1927,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1929,7 +1937,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>11:01</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1956,7 +1969,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131009284</v>
+        <v>131009289</v>
       </c>
       <c r="B13" t="n">
         <v>57884</v>
@@ -1999,10 +2012,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>589966</v>
+        <v>589785</v>
       </c>
       <c r="R13" t="n">
-        <v>6911126</v>
+        <v>6911221</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2034,7 +2047,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2044,7 +2057,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2076,53 +2089,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131009289</v>
+        <v>131009303</v>
       </c>
       <c r="B14" t="n">
-        <v>57884</v>
+        <v>80253</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Grössjöbergen, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>589785</v>
+        <v>589748</v>
       </c>
       <c r="R14" t="n">
-        <v>6911221</v>
+        <v>6911130</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2154,7 +2159,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2164,12 +2169,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:42</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>färska ringhack på tall</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2916,10 +2916,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131009305</v>
+        <v>131009308</v>
       </c>
       <c r="B21" t="n">
-        <v>57884</v>
+        <v>79244</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2927,42 +2927,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Grössjöbergen, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>589757</v>
+        <v>589686</v>
       </c>
       <c r="R21" t="n">
-        <v>6911178</v>
+        <v>6911077</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2994,7 +2986,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3004,12 +2996,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:43</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>färska ringhack på tall</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3036,7 +3023,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131009498</v>
+        <v>131009305</v>
       </c>
       <c r="B22" t="n">
         <v>57884</v>
@@ -3079,10 +3066,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>589629</v>
+        <v>589757</v>
       </c>
       <c r="R22" t="n">
-        <v>6911040</v>
+        <v>6911178</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3114,7 +3101,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3124,7 +3111,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -3156,10 +3143,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131009308</v>
+        <v>131009498</v>
       </c>
       <c r="B23" t="n">
-        <v>79243</v>
+        <v>57884</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3167,34 +3154,42 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Grössjöbergen, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>589686</v>
+        <v>589629</v>
       </c>
       <c r="R23" t="n">
-        <v>6911077</v>
+        <v>6911040</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3226,7 +3221,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3236,7 +3231,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:02</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3865,7 +3865,7 @@
         <v>131009285</v>
       </c>
       <c r="B29" t="n">
-        <v>80252</v>
+        <v>80253</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4692,7 +4692,7 @@
         <v>131009273</v>
       </c>
       <c r="B36" t="n">
-        <v>79243</v>
+        <v>79244</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5039,7 +5039,7 @@
         <v>131009291</v>
       </c>
       <c r="B39" t="n">
-        <v>80252</v>
+        <v>80253</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5266,7 +5266,7 @@
         <v>131009290</v>
       </c>
       <c r="B41" t="n">
-        <v>80221</v>
+        <v>80222</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 2486-2026 artfynd.xlsx
+++ b/artfynd/A 2486-2026 artfynd.xlsx
@@ -1849,53 +1849,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131009284</v>
+        <v>131009303</v>
       </c>
       <c r="B12" t="n">
-        <v>57884</v>
+        <v>80253</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Grössjöbergen, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>589966</v>
+        <v>589748</v>
       </c>
       <c r="R12" t="n">
-        <v>6911126</v>
+        <v>6911130</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1927,7 +1919,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1937,12 +1929,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:01</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>färska ringhack på tall</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1969,7 +1956,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131009289</v>
+        <v>131009284</v>
       </c>
       <c r="B13" t="n">
         <v>57884</v>
@@ -2012,10 +1999,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>589785</v>
+        <v>589966</v>
       </c>
       <c r="R13" t="n">
-        <v>6911221</v>
+        <v>6911126</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2047,7 +2034,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2057,7 +2044,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2089,45 +2076,53 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131009303</v>
+        <v>131009289</v>
       </c>
       <c r="B14" t="n">
-        <v>80253</v>
+        <v>57884</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Grössjöbergen, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>589748</v>
+        <v>589785</v>
       </c>
       <c r="R14" t="n">
-        <v>6911130</v>
+        <v>6911221</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2159,7 +2154,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2169,7 +2164,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>10:42</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2916,10 +2916,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131009308</v>
+        <v>131009305</v>
       </c>
       <c r="B21" t="n">
-        <v>79244</v>
+        <v>57884</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2927,34 +2927,42 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Grössjöbergen, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>589686</v>
+        <v>589757</v>
       </c>
       <c r="R21" t="n">
-        <v>6911077</v>
+        <v>6911178</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2986,7 +2994,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2996,7 +3004,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:43</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3023,7 +3036,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131009305</v>
+        <v>131009498</v>
       </c>
       <c r="B22" t="n">
         <v>57884</v>
@@ -3066,10 +3079,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>589757</v>
+        <v>589629</v>
       </c>
       <c r="R22" t="n">
-        <v>6911178</v>
+        <v>6911040</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3101,7 +3114,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3111,7 +3124,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -3143,10 +3156,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131009498</v>
+        <v>131009308</v>
       </c>
       <c r="B23" t="n">
-        <v>57884</v>
+        <v>79244</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3154,42 +3167,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Grössjöbergen, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>589629</v>
+        <v>589686</v>
       </c>
       <c r="R23" t="n">
-        <v>6911040</v>
+        <v>6911077</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3221,7 +3226,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3231,12 +3236,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>09:02</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>färska ringhack på tall</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3862,45 +3862,53 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131009285</v>
+        <v>131009302</v>
       </c>
       <c r="B29" t="n">
-        <v>80253</v>
+        <v>57884</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Grössjöbergen, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>589879</v>
+        <v>589716</v>
       </c>
       <c r="R29" t="n">
-        <v>6911153</v>
+        <v>6911140</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3932,7 +3940,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3942,7 +3950,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:54</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3969,7 +3982,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131009302</v>
+        <v>131009306</v>
       </c>
       <c r="B30" t="n">
         <v>57884</v>
@@ -4012,10 +4025,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>589716</v>
+        <v>589791</v>
       </c>
       <c r="R30" t="n">
-        <v>6911140</v>
+        <v>6911148</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4047,7 +4060,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4057,12 +4070,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>färska ringhack på tall</t>
+          <t>färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4089,53 +4102,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131009306</v>
+        <v>131009285</v>
       </c>
       <c r="B31" t="n">
-        <v>57884</v>
+        <v>80253</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Grössjöbergen, Mpd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>589791</v>
+        <v>589879</v>
       </c>
       <c r="R31" t="n">
-        <v>6911148</v>
+        <v>6911153</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4167,7 +4172,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4177,12 +4182,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>09:38</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>färska och äldre ringhack på tall</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD31" t="b">

--- a/artfynd/A 2486-2026 artfynd.xlsx
+++ b/artfynd/A 2486-2026 artfynd.xlsx
@@ -1849,45 +1849,53 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131009303</v>
+        <v>131009284</v>
       </c>
       <c r="B12" t="n">
-        <v>80253</v>
+        <v>57884</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Grössjöbergen, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>589748</v>
+        <v>589966</v>
       </c>
       <c r="R12" t="n">
-        <v>6911130</v>
+        <v>6911126</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1919,7 +1927,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1929,7 +1937,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>11:01</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1956,7 +1969,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131009284</v>
+        <v>131009289</v>
       </c>
       <c r="B13" t="n">
         <v>57884</v>
@@ -1999,10 +2012,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>589966</v>
+        <v>589785</v>
       </c>
       <c r="R13" t="n">
-        <v>6911126</v>
+        <v>6911221</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2034,7 +2047,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2044,7 +2057,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2076,53 +2089,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131009289</v>
+        <v>131009303</v>
       </c>
       <c r="B14" t="n">
-        <v>57884</v>
+        <v>80253</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Grössjöbergen, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>589785</v>
+        <v>589748</v>
       </c>
       <c r="R14" t="n">
-        <v>6911221</v>
+        <v>6911130</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2154,7 +2159,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2164,12 +2169,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:42</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>färska ringhack på tall</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2916,10 +2916,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131009305</v>
+        <v>131009308</v>
       </c>
       <c r="B21" t="n">
-        <v>57884</v>
+        <v>79244</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2927,42 +2927,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Grössjöbergen, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>589757</v>
+        <v>589686</v>
       </c>
       <c r="R21" t="n">
-        <v>6911178</v>
+        <v>6911077</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2994,7 +2986,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3004,12 +2996,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:43</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>färska ringhack på tall</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3036,7 +3023,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131009498</v>
+        <v>131009305</v>
       </c>
       <c r="B22" t="n">
         <v>57884</v>
@@ -3079,10 +3066,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>589629</v>
+        <v>589757</v>
       </c>
       <c r="R22" t="n">
-        <v>6911040</v>
+        <v>6911178</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3114,7 +3101,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3124,7 +3111,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -3156,10 +3143,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131009308</v>
+        <v>131009498</v>
       </c>
       <c r="B23" t="n">
-        <v>79244</v>
+        <v>57884</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3167,34 +3154,42 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Grössjöbergen, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>589686</v>
+        <v>589629</v>
       </c>
       <c r="R23" t="n">
-        <v>6911077</v>
+        <v>6911040</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3226,7 +3221,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3236,7 +3231,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:02</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -5036,45 +5036,53 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131009291</v>
+        <v>131009275</v>
       </c>
       <c r="B39" t="n">
-        <v>80253</v>
+        <v>57884</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Grössjöbergen, Mpd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>589791</v>
+        <v>589844</v>
       </c>
       <c r="R39" t="n">
-        <v>6911200</v>
+        <v>6911365</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5106,7 +5114,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5116,7 +5124,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>11:53</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5143,53 +5156,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131009275</v>
+        <v>131009291</v>
       </c>
       <c r="B40" t="n">
-        <v>57884</v>
+        <v>80253</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Grössjöbergen, Mpd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>589844</v>
+        <v>589791</v>
       </c>
       <c r="R40" t="n">
-        <v>6911365</v>
+        <v>6911200</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5221,7 +5226,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5231,12 +5236,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:53</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>färska ringhack på tall</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD40" t="b">

--- a/artfynd/A 2486-2026 artfynd.xlsx
+++ b/artfynd/A 2486-2026 artfynd.xlsx
@@ -915,53 +915,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131009298</v>
+        <v>131009286</v>
       </c>
       <c r="B4" t="n">
-        <v>57884</v>
+        <v>80253</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Grössjöbergen, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>589735</v>
+        <v>589865</v>
       </c>
       <c r="R4" t="n">
-        <v>6911227</v>
+        <v>6911173</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,7 +985,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1003,12 +995,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:12</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>färska ringhack på tall</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1035,7 +1022,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131009294</v>
+        <v>131009298</v>
       </c>
       <c r="B5" t="n">
         <v>57884</v>
@@ -1078,10 +1065,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>589787</v>
+        <v>589735</v>
       </c>
       <c r="R5" t="n">
-        <v>6911183</v>
+        <v>6911227</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1113,7 +1100,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1123,7 +1110,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1155,45 +1142,53 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131009286</v>
+        <v>131009294</v>
       </c>
       <c r="B6" t="n">
-        <v>80253</v>
+        <v>57884</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Grössjöbergen, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>589865</v>
+        <v>589787</v>
       </c>
       <c r="R6" t="n">
-        <v>6911173</v>
+        <v>6911183</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1225,7 +1220,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1235,7 +1230,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:24</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1849,53 +1849,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131009284</v>
+        <v>131009303</v>
       </c>
       <c r="B12" t="n">
-        <v>57884</v>
+        <v>80253</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Grössjöbergen, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>589966</v>
+        <v>589748</v>
       </c>
       <c r="R12" t="n">
-        <v>6911126</v>
+        <v>6911130</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1927,7 +1919,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1937,12 +1929,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:01</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>färska ringhack på tall</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2089,45 +2076,53 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131009303</v>
+        <v>131009284</v>
       </c>
       <c r="B14" t="n">
-        <v>80253</v>
+        <v>57884</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Grössjöbergen, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>589748</v>
+        <v>589966</v>
       </c>
       <c r="R14" t="n">
-        <v>6911130</v>
+        <v>6911126</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2159,7 +2154,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2169,7 +2164,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>11:01</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -3862,53 +3862,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131009302</v>
+        <v>131009285</v>
       </c>
       <c r="B29" t="n">
-        <v>57884</v>
+        <v>80253</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Grössjöbergen, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>589716</v>
+        <v>589879</v>
       </c>
       <c r="R29" t="n">
-        <v>6911140</v>
+        <v>6911153</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3940,7 +3932,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3950,12 +3942,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>09:54</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>färska ringhack på tall</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3982,7 +3969,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131009306</v>
+        <v>131009302</v>
       </c>
       <c r="B30" t="n">
         <v>57884</v>
@@ -4025,10 +4012,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>589791</v>
+        <v>589716</v>
       </c>
       <c r="R30" t="n">
-        <v>6911148</v>
+        <v>6911140</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4060,7 +4047,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4070,12 +4057,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>färska och äldre ringhack på tall</t>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4102,45 +4089,53 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131009285</v>
+        <v>131009306</v>
       </c>
       <c r="B31" t="n">
-        <v>80253</v>
+        <v>57884</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Grössjöbergen, Mpd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>589879</v>
+        <v>589791</v>
       </c>
       <c r="R31" t="n">
-        <v>6911153</v>
+        <v>6911148</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4172,7 +4167,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4182,7 +4177,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:38</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD31" t="b">

--- a/artfynd/A 2486-2026 artfynd.xlsx
+++ b/artfynd/A 2486-2026 artfynd.xlsx
@@ -1956,7 +1956,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131009289</v>
+        <v>131009284</v>
       </c>
       <c r="B13" t="n">
         <v>57884</v>
@@ -1999,10 +1999,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>589785</v>
+        <v>589966</v>
       </c>
       <c r="R13" t="n">
-        <v>6911221</v>
+        <v>6911126</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2076,7 +2076,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131009284</v>
+        <v>131009289</v>
       </c>
       <c r="B14" t="n">
         <v>57884</v>
@@ -2119,10 +2119,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>589966</v>
+        <v>589785</v>
       </c>
       <c r="R14" t="n">
-        <v>6911126</v>
+        <v>6911221</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2154,7 +2154,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2916,10 +2916,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131009308</v>
+        <v>131009305</v>
       </c>
       <c r="B21" t="n">
-        <v>79244</v>
+        <v>57884</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2927,34 +2927,42 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Grössjöbergen, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>589686</v>
+        <v>589757</v>
       </c>
       <c r="R21" t="n">
-        <v>6911077</v>
+        <v>6911178</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2986,7 +2994,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2996,7 +3004,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:43</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3023,7 +3036,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131009305</v>
+        <v>131009498</v>
       </c>
       <c r="B22" t="n">
         <v>57884</v>
@@ -3066,10 +3079,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>589757</v>
+        <v>589629</v>
       </c>
       <c r="R22" t="n">
-        <v>6911178</v>
+        <v>6911040</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3101,7 +3114,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3111,7 +3124,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -3143,10 +3156,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131009498</v>
+        <v>131009304</v>
       </c>
       <c r="B23" t="n">
-        <v>57884</v>
+        <v>58043</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3154,29 +3167,33 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
@@ -3186,10 +3203,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>589629</v>
+        <v>589753</v>
       </c>
       <c r="R23" t="n">
-        <v>6911040</v>
+        <v>6911167</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3221,7 +3238,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3231,12 +3248,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>09:02</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>färska ringhack på tall</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3263,10 +3275,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131009304</v>
+        <v>131009308</v>
       </c>
       <c r="B24" t="n">
-        <v>58043</v>
+        <v>79244</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3274,46 +3286,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Grössjöbergen, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>589753</v>
+        <v>589686</v>
       </c>
       <c r="R24" t="n">
-        <v>6911167</v>
+        <v>6911077</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3345,7 +3345,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3355,7 +3355,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD24" t="b">

--- a/artfynd/A 2486-2026 artfynd.xlsx
+++ b/artfynd/A 2486-2026 artfynd.xlsx
@@ -918,7 +918,7 @@
         <v>131009286</v>
       </c>
       <c r="B4" t="n">
-        <v>80253</v>
+        <v>80254</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>131009283</v>
       </c>
       <c r="B7" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1852,7 +1852,7 @@
         <v>131009303</v>
       </c>
       <c r="B12" t="n">
-        <v>80253</v>
+        <v>80254</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         <v>131009308</v>
       </c>
       <c r="B24" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3862,45 +3862,53 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131009285</v>
+        <v>131009302</v>
       </c>
       <c r="B29" t="n">
-        <v>80253</v>
+        <v>57884</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Grössjöbergen, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>589879</v>
+        <v>589716</v>
       </c>
       <c r="R29" t="n">
-        <v>6911153</v>
+        <v>6911140</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3932,7 +3940,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3942,7 +3950,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:54</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3969,7 +3982,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131009302</v>
+        <v>131009306</v>
       </c>
       <c r="B30" t="n">
         <v>57884</v>
@@ -4012,10 +4025,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>589716</v>
+        <v>589791</v>
       </c>
       <c r="R30" t="n">
-        <v>6911140</v>
+        <v>6911148</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4047,7 +4060,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4057,12 +4070,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>färska ringhack på tall</t>
+          <t>färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4089,53 +4102,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131009306</v>
+        <v>131009285</v>
       </c>
       <c r="B31" t="n">
-        <v>57884</v>
+        <v>80254</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Grössjöbergen, Mpd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>589791</v>
+        <v>589879</v>
       </c>
       <c r="R31" t="n">
-        <v>6911148</v>
+        <v>6911153</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4167,7 +4172,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4177,12 +4182,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>09:38</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>färska och äldre ringhack på tall</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4692,7 +4692,7 @@
         <v>131009273</v>
       </c>
       <c r="B36" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5036,53 +5036,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131009275</v>
+        <v>131009291</v>
       </c>
       <c r="B39" t="n">
-        <v>57884</v>
+        <v>80254</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Grössjöbergen, Mpd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>589844</v>
+        <v>589791</v>
       </c>
       <c r="R39" t="n">
-        <v>6911365</v>
+        <v>6911200</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5114,7 +5106,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5124,12 +5116,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:53</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>färska ringhack på tall</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5156,45 +5143,53 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131009291</v>
+        <v>131009275</v>
       </c>
       <c r="B40" t="n">
-        <v>80253</v>
+        <v>57884</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Grössjöbergen, Mpd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>589791</v>
+        <v>589844</v>
       </c>
       <c r="R40" t="n">
-        <v>6911200</v>
+        <v>6911365</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5226,7 +5221,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5236,7 +5231,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>11:53</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5266,7 +5266,7 @@
         <v>131009290</v>
       </c>
       <c r="B41" t="n">
-        <v>80222</v>
+        <v>80223</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 2486-2026 artfynd.xlsx
+++ b/artfynd/A 2486-2026 artfynd.xlsx
@@ -2916,10 +2916,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131009305</v>
+        <v>131009308</v>
       </c>
       <c r="B21" t="n">
-        <v>57884</v>
+        <v>79245</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2927,42 +2927,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Grössjöbergen, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>589757</v>
+        <v>589686</v>
       </c>
       <c r="R21" t="n">
-        <v>6911178</v>
+        <v>6911077</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2994,7 +2986,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3004,12 +2996,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:43</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>färska ringhack på tall</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3036,7 +3023,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131009498</v>
+        <v>131009305</v>
       </c>
       <c r="B22" t="n">
         <v>57884</v>
@@ -3079,10 +3066,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>589629</v>
+        <v>589757</v>
       </c>
       <c r="R22" t="n">
-        <v>6911040</v>
+        <v>6911178</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3114,7 +3101,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3124,7 +3111,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -3156,10 +3143,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131009304</v>
+        <v>131009498</v>
       </c>
       <c r="B23" t="n">
-        <v>58043</v>
+        <v>57884</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3167,33 +3154,29 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
@@ -3203,10 +3186,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>589753</v>
+        <v>589629</v>
       </c>
       <c r="R23" t="n">
-        <v>6911167</v>
+        <v>6911040</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3238,7 +3221,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3248,7 +3231,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:02</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3275,10 +3263,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131009308</v>
+        <v>131009304</v>
       </c>
       <c r="B24" t="n">
-        <v>79245</v>
+        <v>58043</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3286,34 +3274,46 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Grössjöbergen, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>589686</v>
+        <v>589753</v>
       </c>
       <c r="R24" t="n">
-        <v>6911077</v>
+        <v>6911167</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3345,7 +3345,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3355,7 +3355,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD24" t="b">
